--- a/data/trans_orig/P57_AF_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57_AF_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2007</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>438102</t>
+          <t>439944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>486644</t>
+          <t>491666</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>435418</t>
+          <t>440382</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>487033</t>
+          <t>488492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>891400</t>
+          <t>890774</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>961809</t>
+          <t>959489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>207368</t>
+          <t>202346</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255910</t>
+          <t>254068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>200323</t>
+          <t>198864</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251938</t>
+          <t>246974</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>419559</t>
+          <t>421879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>489968</t>
+          <t>490594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>544442</t>
+          <t>546013</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>611515</t>
+          <t>607007</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>573170</t>
+          <t>570659</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>636381</t>
+          <t>632205</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1139265</t>
+          <t>1138045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1221350</t>
+          <t>1230675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>353709</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416274</t>
+          <t>414703</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>332012</t>
+          <t>336188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>395223</t>
+          <t>397734</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>707759</t>
+          <t>698434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>789844</t>
+          <t>791064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>356371</t>
+          <t>358950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>408058</t>
+          <t>411438</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>375791</t>
+          <t>372200</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>424970</t>
+          <t>421935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>741239</t>
+          <t>745278</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>815852</t>
+          <t>816972</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,05%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268700</t>
+          <t>265320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320387</t>
+          <t>317808</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258871</t>
+          <t>261906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>308050</t>
+          <t>311641</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>544747</t>
+          <t>543627</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>619360</t>
+          <t>615321</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>531451</t>
+          <t>528117</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>589837</t>
+          <t>585895</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>571760</t>
+          <t>572824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>635593</t>
+          <t>633149</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1120617</t>
+          <t>1118147</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1204600</t>
+          <t>1206274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>350704</t>
+          <t>354646</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>409090</t>
+          <t>412424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>402039</t>
+          <t>404483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465872</t>
+          <t>464808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>773573</t>
+          <t>771899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>857556</t>
+          <t>860026</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1935520</t>
+          <t>1931499</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2047449</t>
+          <t>2040308</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2009712</t>
+          <t>2014386</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2120774</t>
+          <t>2124563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3977174</t>
+          <t>3970701</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4128712</t>
+          <t>4129880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1224577</t>
+          <t>1231718</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1336506</t>
+          <t>1340527</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1256448</t>
+          <t>1252659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1367510</t>
+          <t>1362836</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2520536</t>
+          <t>2519368</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2672074</t>
+          <t>2678547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2012</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2012 (tasa de respuesta: 99,34%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>371808</t>
+          <t>371447</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>423514</t>
+          <t>426518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>411101</t>
+          <t>412007</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>464133</t>
+          <t>465242</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>798098</t>
+          <t>796844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>871581</t>
+          <t>873331</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275134</t>
+          <t>272130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>326840</t>
+          <t>327201</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>227218</t>
+          <t>226109</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280250</t>
+          <t>279344</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518418</t>
+          <t>516668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>591901</t>
+          <t>593155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>595798</t>
+          <t>595855</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>660515</t>
+          <t>662375</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>661294</t>
+          <t>660923</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>725278</t>
+          <t>723879</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1274923</t>
+          <t>1279595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1366413</t>
+          <t>1366354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353336</t>
+          <t>351476</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418053</t>
+          <t>417996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300575</t>
+          <t>301974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364559</t>
+          <t>364930</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>673290</t>
+          <t>673349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>764780</t>
+          <t>760108</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>418057</t>
+          <t>416570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>473557</t>
+          <t>474606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>453496</t>
+          <t>452013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>509326</t>
+          <t>506236</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>887774</t>
+          <t>883710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>965075</t>
+          <t>966641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276828</t>
+          <t>275779</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>332328</t>
+          <t>333815</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>265706</t>
+          <t>268796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321536</t>
+          <t>323019</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>560341</t>
+          <t>558775</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>637642</t>
+          <t>641706</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>605553</t>
+          <t>605836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>664152</t>
+          <t>664595</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>719281</t>
+          <t>717641</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>774817</t>
+          <t>777637</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1340742</t>
+          <t>1338846</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1424166</t>
+          <t>1425766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,91%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>278717</t>
+          <t>278274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>337316</t>
+          <t>337033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264937</t>
+          <t>262117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>320473</t>
+          <t>322113</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>558456</t>
+          <t>556856</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>641880</t>
+          <t>643776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2047014</t>
+          <t>2049151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2164819</t>
+          <t>2166148</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2303002</t>
+          <t>2300373</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2419673</t>
+          <t>2417984</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4389377</t>
+          <t>4388709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4546755</t>
+          <t>4554484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,65%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1240934</t>
+          <t>1239605</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1358739</t>
+          <t>1356602</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1112315</t>
+          <t>1114004</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1228986</t>
+          <t>1231615</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2390986</t>
+          <t>2383257</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2548364</t>
+          <t>2549032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2016</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>470907</t>
+          <t>472198</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>517921</t>
+          <t>519715</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>498105</t>
+          <t>495541</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>541910</t>
+          <t>540096</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>986650</t>
+          <t>987127</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1049646</t>
+          <t>1049384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,21%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>154875</t>
+          <t>153081</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>201889</t>
+          <t>200598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127052</t>
+          <t>128866</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>170857</t>
+          <t>173421</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>292112</t>
+          <t>292374</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>355108</t>
+          <t>354631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>722667</t>
+          <t>717371</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>777609</t>
+          <t>778208</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>773882</t>
+          <t>771677</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>826120</t>
+          <t>827459</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1509043</t>
+          <t>1509270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1590450</t>
+          <t>1592840</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>242715</t>
+          <t>242116</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>297657</t>
+          <t>302953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>211651</t>
+          <t>210312</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>263889</t>
+          <t>266094</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>467646</t>
+          <t>465256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>549053</t>
+          <t>548826</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>587809</t>
+          <t>584767</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>629811</t>
+          <t>628986</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,82 +5328,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>83,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>638221</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>614778</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>658598</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>82,06%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>79,04%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>84,68%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1154</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1247914</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1218773</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>1279127</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>81,45%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>79,54%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>83,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>638221</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>615877</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>658922</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>82,06%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>79,19%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>84,72%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1247914</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1216203</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1276481</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>81,45%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>79,38%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124609</t>
+          <t>125434</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166611</t>
+          <t>169653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,82 +5441,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>16,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>22,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>139549</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>119172</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>162992</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>17,94%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>15,32%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>20,96%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>284276</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>253063</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>313417</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>18,55%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>16,52%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>22,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>139549</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>118848</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>161893</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>15,28%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>20,81%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>284276</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>255709</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>315987</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>18,55%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>16,69%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>616834</t>
+          <t>614853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>670008</t>
+          <t>669962</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>693937</t>
+          <t>693297</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>757345</t>
+          <t>756072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1323759</t>
+          <t>1322709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1409362</t>
+          <t>1402652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>261477</t>
+          <t>261523</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>314651</t>
+          <t>316632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284052</t>
+          <t>285325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>347460</t>
+          <t>348100</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>563520</t>
+          <t>570230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>649123</t>
+          <t>650173</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2443440</t>
+          <t>2446255</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2549433</t>
+          <t>2549832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2628925</t>
+          <t>2632941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2732085</t>
+          <t>2732581</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5110015</t>
+          <t>5108940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5256477</t>
+          <t>5254090</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>829591</t>
+          <t>829192</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>935584</t>
+          <t>932769</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>793816</t>
+          <t>793320</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>896976</t>
+          <t>892960</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1648449</t>
+          <t>1650836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1794911</t>
+          <t>1795986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2023</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2023 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>291465</t>
+          <t>290805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>344600</t>
+          <t>346594</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>352334</t>
+          <t>352247</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>393714</t>
+          <t>393175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>658523</t>
+          <t>658359</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>725998</t>
+          <t>730336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283548</t>
+          <t>281554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>336683</t>
+          <t>337343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274856</t>
+          <t>275395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>316236</t>
+          <t>316323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>570721</t>
+          <t>566383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>638196</t>
+          <t>638360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,23%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>296792</t>
+          <t>295269</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>695541</t>
+          <t>700215</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>552452</t>
+          <t>553604</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>606376</t>
+          <t>605467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>761065</t>
+          <t>781264</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1284199</t>
+          <t>1283251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,1%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490361</t>
+          <t>485687</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>889110</t>
+          <t>890633</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343042</t>
+          <t>343951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>396966</t>
+          <t>395814</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>851121</t>
+          <t>852069</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1374255</t>
+          <t>1354056</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,41%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>385062</t>
+          <t>384043</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>447347</t>
+          <t>445264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>491257</t>
+          <t>492748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>759945</t>
+          <t>765968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>915955</t>
+          <t>911460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1259807</t>
+          <t>1247314</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,36%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>255883</t>
+          <t>257966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318168</t>
+          <t>319187</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170326</t>
+          <t>164303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>439014</t>
+          <t>437523</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373694</t>
+          <t>386187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>717546</t>
+          <t>722041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>470124</t>
+          <t>469208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>536356</t>
+          <t>538508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>428946</t>
+          <t>440183</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>607215</t>
+          <t>605960</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>930075</t>
+          <t>929815</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1116448</t>
+          <t>1118069</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>379900</t>
+          <t>377748</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>446132</t>
+          <t>447048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>474048</t>
+          <t>475303</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>652317</t>
+          <t>641080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>881071</t>
+          <t>879450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1067444</t>
+          <t>1067704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,45%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1347645</t>
+          <t>1388323</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1940319</t>
+          <t>1943104</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1982363</t>
+          <t>1978061</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2366368</t>
+          <t>2390665</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3491972</t>
+          <t>3491842</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4156024</t>
+          <t>4185170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,25%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1493217</t>
+          <t>1490432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2085891</t>
+          <t>2045213</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1263154</t>
+          <t>1238857</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1647159</t>
+          <t>1651461</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2907034</t>
+          <t>2877888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3571086</t>
+          <t>3571216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/P57_AF_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57_AF_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>439944</t>
+          <t>441341</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>491666</t>
+          <t>489741</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>440382</t>
+          <t>437451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>488492</t>
+          <t>486430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>890774</t>
+          <t>890998</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>959489</t>
+          <t>961798</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>202346</t>
+          <t>204271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>254068</t>
+          <t>252671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198864</t>
+          <t>200926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246974</t>
+          <t>249905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>421879</t>
+          <t>419570</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>490594</t>
+          <t>490370</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>546013</t>
+          <t>549263</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>607007</t>
+          <t>610374</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>570659</t>
+          <t>572863</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>632205</t>
+          <t>634996</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1138045</t>
+          <t>1132304</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1230675</t>
+          <t>1221664</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353709</t>
+          <t>350342</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414703</t>
+          <t>411453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336188</t>
+          <t>333397</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>397734</t>
+          <t>395530</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>698434</t>
+          <t>707445</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>791064</t>
+          <t>796805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>358950</t>
+          <t>356025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>411438</t>
+          <t>411296</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>372200</t>
+          <t>373642</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>421935</t>
+          <t>421269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>745278</t>
+          <t>745046</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>816972</t>
+          <t>818877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>265320</t>
+          <t>265462</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317808</t>
+          <t>320733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>261906</t>
+          <t>262572</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>311641</t>
+          <t>310199</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543627</t>
+          <t>541722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>615321</t>
+          <t>615553</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>528117</t>
+          <t>529017</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>585895</t>
+          <t>587550</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>572824</t>
+          <t>572896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>633149</t>
+          <t>635836</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1118147</t>
+          <t>1119773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1206274</t>
+          <t>1209643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>354646</t>
+          <t>352991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>412424</t>
+          <t>411524</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>404483</t>
+          <t>401796</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>464808</t>
+          <t>464736</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>771899</t>
+          <t>768530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>860026</t>
+          <t>858400</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1931499</t>
+          <t>1929022</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2040308</t>
+          <t>2039205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2014386</t>
+          <t>2014582</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2124563</t>
+          <t>2123827</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3970701</t>
+          <t>3973465</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4129880</t>
+          <t>4136987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1231718</t>
+          <t>1232821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1340527</t>
+          <t>1343004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1252659</t>
+          <t>1253395</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1362836</t>
+          <t>1362640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2519368</t>
+          <t>2512261</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2678547</t>
+          <t>2675783</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>371447</t>
+          <t>370337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>426518</t>
+          <t>424962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>412007</t>
+          <t>409363</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>465242</t>
+          <t>464890</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>796844</t>
+          <t>802546</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>873331</t>
+          <t>873784</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,86%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>272130</t>
+          <t>273686</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>327201</t>
+          <t>328311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>226109</t>
+          <t>226461</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279344</t>
+          <t>281988</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516668</t>
+          <t>516215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>593155</t>
+          <t>587453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>595855</t>
+          <t>596930</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>662375</t>
+          <t>659634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>660923</t>
+          <t>662043</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>723879</t>
+          <t>723567</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1279595</t>
+          <t>1280729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1366354</t>
+          <t>1365834</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,96%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351476</t>
+          <t>354217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417996</t>
+          <t>416921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>301974</t>
+          <t>302286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364930</t>
+          <t>363810</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>673349</t>
+          <t>673869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>760108</t>
+          <t>758974</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>416570</t>
+          <t>418153</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>474606</t>
+          <t>474571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>452013</t>
+          <t>451621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>506236</t>
+          <t>508955</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>883710</t>
+          <t>885157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>966641</t>
+          <t>966709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275779</t>
+          <t>275814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>333815</t>
+          <t>332232</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>268796</t>
+          <t>266077</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323019</t>
+          <t>323411</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>558775</t>
+          <t>558707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641706</t>
+          <t>640259</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>41,97%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>605836</t>
+          <t>605117</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>664595</t>
+          <t>665068</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>717641</t>
+          <t>715106</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>777637</t>
+          <t>777338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1338846</t>
+          <t>1338989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1425766</t>
+          <t>1424508</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,85%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>278274</t>
+          <t>277801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>337033</t>
+          <t>337752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>262117</t>
+          <t>262416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>322113</t>
+          <t>324648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>556856</t>
+          <t>558114</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>643776</t>
+          <t>643633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2049151</t>
+          <t>2056241</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2166148</t>
+          <t>2169055</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2300373</t>
+          <t>2301178</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2417984</t>
+          <t>2417346</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4388709</t>
+          <t>4383012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4554484</t>
+          <t>4554313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1239605</t>
+          <t>1236698</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1356602</t>
+          <t>1349512</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1114004</t>
+          <t>1114642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1231615</t>
+          <t>1230810</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2383257</t>
+          <t>2383428</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2549032</t>
+          <t>2554729</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>472198</t>
+          <t>472197</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>519715</t>
+          <t>518385</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>495541</t>
+          <t>498636</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>540096</t>
+          <t>541913</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>987127</t>
+          <t>984118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1049384</t>
+          <t>1049974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>153081</t>
+          <t>154411</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>200598</t>
+          <t>200599</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>128866</t>
+          <t>127049</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>173421</t>
+          <t>170326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>292374</t>
+          <t>291784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>354631</t>
+          <t>357640</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>717371</t>
+          <t>721325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>778208</t>
+          <t>778879</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>771677</t>
+          <t>771889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>827459</t>
+          <t>827991</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1509270</t>
+          <t>1507072</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1592840</t>
+          <t>1588589</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,19%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>242116</t>
+          <t>241445</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>302953</t>
+          <t>298999</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210312</t>
+          <t>209780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>266094</t>
+          <t>265882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>465256</t>
+          <t>469507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>548826</t>
+          <t>551024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>584767</t>
+          <t>583497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>628986</t>
+          <t>630033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>614778</t>
+          <t>617246</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>658598</t>
+          <t>658924</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1218773</t>
+          <t>1217906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1279127</t>
+          <t>1278796</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125434</t>
+          <t>124387</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>169653</t>
+          <t>170923</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119172</t>
+          <t>118846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162992</t>
+          <t>160524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>253063</t>
+          <t>253394</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>313417</t>
+          <t>314284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>614853</t>
+          <t>612348</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>669962</t>
+          <t>668648</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>693297</t>
+          <t>693664</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>756072</t>
+          <t>753578</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1322709</t>
+          <t>1321399</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1402652</t>
+          <t>1404625</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>261523</t>
+          <t>262837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>316632</t>
+          <t>319137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>285325</t>
+          <t>287819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348100</t>
+          <t>347733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>570230</t>
+          <t>568257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>650173</t>
+          <t>651483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2446255</t>
+          <t>2444893</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2549832</t>
+          <t>2550717</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2632941</t>
+          <t>2627909</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2732581</t>
+          <t>2732923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5108940</t>
+          <t>5114418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5254090</t>
+          <t>5252865</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,07%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>829192</t>
+          <t>828307</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>932769</t>
+          <t>934131</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>793320</t>
+          <t>792978</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>892960</t>
+          <t>897992</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1650836</t>
+          <t>1652061</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1795986</t>
+          <t>1790508</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>320299</t>
+          <t>358976</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>290805</t>
+          <t>332277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>346594</t>
+          <t>387975</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>373127</t>
+          <t>405353</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>352247</t>
+          <t>381585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>393175</t>
+          <t>425769</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>693427</t>
+          <t>764329</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>658359</t>
+          <t>728306</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>730336</t>
+          <t>799125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,72%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>307849</t>
+          <t>324257</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281554</t>
+          <t>295258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>337343</t>
+          <t>350956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>295443</t>
+          <t>320282</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275395</t>
+          <t>299866</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>316323</t>
+          <t>344050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>603292</t>
+          <t>644539</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>566383</t>
+          <t>609743</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>638360</t>
+          <t>680562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>628148</t>
+          <t>683233</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>628148</t>
+          <t>683233</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>628148</t>
+          <t>683233</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>668570</t>
+          <t>725635</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>668570</t>
+          <t>725635</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>668570</t>
+          <t>725635</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1296719</t>
+          <t>1408868</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1296719</t>
+          <t>1408868</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1296719</t>
+          <t>1408868</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>542745</t>
+          <t>603514</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>295269</t>
+          <t>564496</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>700215</t>
+          <t>639723</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>580763</t>
+          <t>662152</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>553604</t>
+          <t>632052</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>605467</t>
+          <t>693210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1123509</t>
+          <t>1265666</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>781264</t>
+          <t>1217580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1283251</t>
+          <t>1309314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>62,33%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>643157</t>
+          <t>436488</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485687</t>
+          <t>400279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>890633</t>
+          <t>475506</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>368655</t>
+          <t>398507</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343951</t>
+          <t>367449</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>395814</t>
+          <t>428607</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1011811</t>
+          <t>834995</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>852069</t>
+          <t>791347</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1354056</t>
+          <t>883081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1185902</t>
+          <t>1040002</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1185902</t>
+          <t>1040002</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1185902</t>
+          <t>1040002</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>949418</t>
+          <t>1060659</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>949418</t>
+          <t>1060659</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>949418</t>
+          <t>1060659</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2135320</t>
+          <t>2100661</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2135320</t>
+          <t>2100661</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2135320</t>
+          <t>2100661</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>415432</t>
+          <t>484647</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>384043</t>
+          <t>451439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>445264</t>
+          <t>515056</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>606379</t>
+          <t>469614</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>492748</t>
+          <t>443914</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>765968</t>
+          <t>496082</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1021811</t>
+          <t>954261</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>911460</t>
+          <t>911512</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1247314</t>
+          <t>994366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>287798</t>
+          <t>315879</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257966</t>
+          <t>285470</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>319187</t>
+          <t>349087</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>323892</t>
+          <t>338497</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164303</t>
+          <t>312029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>437523</t>
+          <t>364197</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>611690</t>
+          <t>654376</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>386187</t>
+          <t>614271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>722041</t>
+          <t>697125</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,34%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703230</t>
+          <t>800526</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703230</t>
+          <t>800526</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703230</t>
+          <t>800526</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>930271</t>
+          <t>808111</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>930271</t>
+          <t>808111</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>930271</t>
+          <t>808111</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1633501</t>
+          <t>1608637</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1633501</t>
+          <t>1608637</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1633501</t>
+          <t>1608637</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>503298</t>
+          <t>549898</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>469208</t>
+          <t>514293</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>538508</t>
+          <t>580695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>556520</t>
+          <t>615044</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>440183</t>
+          <t>585201</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>605960</t>
+          <t>645754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1059818</t>
+          <t>1164942</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>929815</t>
+          <t>1119062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1118069</t>
+          <t>1211145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>58,12%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>412958</t>
+          <t>429985</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>377748</t>
+          <t>399188</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>447048</t>
+          <t>465590</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>524743</t>
+          <t>489112</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>475303</t>
+          <t>458402</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>641080</t>
+          <t>518955</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>937701</t>
+          <t>919096</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>879450</t>
+          <t>872893</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1067704</t>
+          <t>964976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>916256</t>
+          <t>979883</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>916256</t>
+          <t>979883</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>916256</t>
+          <t>979883</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1081263</t>
+          <t>1104156</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1081263</t>
+          <t>1104156</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1081263</t>
+          <t>1104156</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1997519</t>
+          <t>2084038</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1997519</t>
+          <t>2084038</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1997519</t>
+          <t>2084038</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1781775</t>
+          <t>1997035</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1388323</t>
+          <t>1925935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1943104</t>
+          <t>2061694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2116789</t>
+          <t>2152162</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1978061</t>
+          <t>2093941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2390665</t>
+          <t>2208051</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3898565</t>
+          <t>4149198</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3491842</t>
+          <t>4062573</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4185170</t>
+          <t>4237959</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,84%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1651761</t>
+          <t>1506608</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1490432</t>
+          <t>1441949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2045213</t>
+          <t>1577708</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1512733</t>
+          <t>1546398</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1238857</t>
+          <t>1490509</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1651461</t>
+          <t>1604619</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3164493</t>
+          <t>3053005</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2877888</t>
+          <t>2964244</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3571216</t>
+          <t>3139630</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3433536</t>
+          <t>3503643</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3433536</t>
+          <t>3503643</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3433536</t>
+          <t>3503643</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3629522</t>
+          <t>3698560</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3629522</t>
+          <t>3698560</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3629522</t>
+          <t>3698560</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7063058</t>
+          <t>7202203</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7063058</t>
+          <t>7202203</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7063058</t>
+          <t>7202203</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
